--- a/Practicas Preprofesionales/Editables/horario_practicas.xlsx
+++ b/Practicas Preprofesionales/Editables/horario_practicas.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="11">
   <si>
     <t>Lunes</t>
   </si>
@@ -51,6 +51,12 @@
   </si>
   <si>
     <t>U-LEARNINGCENTER S.A.S</t>
+  </si>
+  <si>
+    <t>Total Horas</t>
+  </si>
+  <si>
+    <t>Horas Semanales</t>
   </si>
 </sst>
 </file>
@@ -128,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -188,11 +194,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -230,6 +247,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -239,7 +260,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,31 +558,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:Q33"/>
+  <dimension ref="C1:Q34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.109375" style="19" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:17" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="17"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
     </row>
     <row r="3" spans="3:17" s="8" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="C3" s="7" t="s">
@@ -563,13 +603,13 @@
         <v>4</v>
       </c>
       <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
     </row>
     <row r="4" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3">
@@ -588,13 +628,13 @@
         <v>29</v>
       </c>
       <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
     </row>
     <row r="5" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C5" s="4" t="s">
@@ -612,17 +652,19 @@
       <c r="G5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H5"/>
-      <c r="I5">
+      <c r="H5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="19">
         <f>6*5</f>
         <v>30</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
     </row>
     <row r="6" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C6" s="5">
@@ -641,13 +683,13 @@
         <v>5</v>
       </c>
       <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
     </row>
     <row r="7" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C7" s="4" t="s">
@@ -665,17 +707,19 @@
       <c r="G7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H7"/>
-      <c r="I7">
+      <c r="H7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="19">
         <f>6*5</f>
         <v>30</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
       <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -695,13 +739,13 @@
         <v>12</v>
       </c>
       <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
     </row>
     <row r="9" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C9" s="4" t="s">
@@ -719,17 +763,19 @@
       <c r="G9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H9"/>
-      <c r="I9">
+      <c r="H9" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="19">
         <f>6*5</f>
         <v>30</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
       <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -749,13 +795,13 @@
         <v>19</v>
       </c>
       <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
     </row>
     <row r="11" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C11" s="4" t="s">
@@ -773,17 +819,19 @@
       <c r="G11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H11"/>
-      <c r="I11">
+      <c r="H11" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="19">
         <f>6*5</f>
         <v>30</v>
       </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -803,13 +851,13 @@
         <v>26</v>
       </c>
       <c r="H12"/>
-      <c r="I12"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
     </row>
     <row r="13" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C13" s="12" t="s">
@@ -827,17 +875,19 @@
       <c r="G13" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H13"/>
-      <c r="I13">
+      <c r="H13" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="19">
         <f>6*5</f>
         <v>30</v>
       </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
       <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -857,13 +907,13 @@
         <v>3</v>
       </c>
       <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
     </row>
     <row r="15" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C15" s="12" t="s">
@@ -881,17 +931,19 @@
       <c r="G15" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H15"/>
-      <c r="I15">
+      <c r="H15" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="19">
         <f>6*5</f>
         <v>30</v>
       </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
       <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -904,20 +956,20 @@
       <c r="E16" s="6">
         <v>8</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="10">
         <v>9</v>
       </c>
       <c r="G16" s="10">
         <v>10</v>
       </c>
       <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="13"/>
     </row>
     <row r="17" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C17" s="12" t="s">
@@ -929,23 +981,24 @@
       <c r="E17" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="14" t="s">
         <v>7</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H17"/>
-      <c r="I17">
-        <f>6*4</f>
-        <v>24</v>
-      </c>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
+      <c r="H17" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="19">
+        <v>18</v>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -965,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
     </row>
     <row r="19" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C19" s="12" t="s">
@@ -989,17 +1042,19 @@
       <c r="G19" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H19"/>
-      <c r="I19">
+      <c r="H19" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="19">
         <f>6*5</f>
         <v>30</v>
       </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
       <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1019,13 +1074,13 @@
         <v>24</v>
       </c>
       <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
     </row>
     <row r="21" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="12" t="s">
@@ -1043,8 +1098,10 @@
       <c r="G21" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H21"/>
-      <c r="I21">
+      <c r="H21" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="19">
         <f>6*5</f>
         <v>30</v>
       </c>
@@ -1056,19 +1113,36 @@
       <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22">
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="19"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="Q22" s="1"/>
+    </row>
+    <row r="23" spans="3:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="20">
         <f>SUM(I5:I21)</f>
-        <v>264</v>
-      </c>
-    </row>
-    <row r="33" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K33" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="34" spans="11:11" x14ac:dyDescent="0.3">
+      <c r="K34" t="s">
         <v>6</v>
       </c>
     </row>
